--- a/Overpotnital/O2 BP/75k/Edited/AB Polyol 1.5bp O2_edited.xlsx
+++ b/Overpotnital/O2 BP/75k/Edited/AB Polyol 1.5bp O2_edited.xlsx
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.599</v>
+        <v>-0.61</v>
       </c>
       <c r="V4" s="0" t="n">
         <v>-6</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.0597</v>
+        <v>-0.0607</v>
       </c>
       <c r="V5" s="0" t="n">
         <v>-5.9</v>
@@ -19192,7 +19192,7 @@
       <c r="C2" s="0" t="n">
         <v>0.846</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="0" t="n">
         <v>0.02188474498689175</v>
       </c>
       <c r="E2" s="0">
@@ -19234,7 +19234,7 @@
       <c r="C3" s="0" t="n">
         <v>0.837</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="0" t="n">
         <v>0.0200420618057251</v>
       </c>
       <c r="E3" s="0">
@@ -19276,7 +19276,7 @@
       <c r="C4" s="0" t="n">
         <v>0.828</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>0.0202435664832592</v>
       </c>
       <c r="E4" s="0">
@@ -19318,7 +19318,7 @@
       <c r="C5" s="0" t="n">
         <v>0.8179999999999999</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="0" t="n">
         <v>0.01856775023043156</v>
       </c>
       <c r="E5" s="0">
@@ -19360,7 +19360,7 @@
       <c r="C6" s="0" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="0" t="n">
         <v>0.02292344346642494</v>
       </c>
       <c r="E6" s="0">
@@ -19402,7 +19402,7 @@
       <c r="C7" s="0" t="n">
         <v>0.803</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="0" t="n">
         <v>0.02005913108587265</v>
       </c>
       <c r="E7" s="0">
@@ -19444,7 +19444,7 @@
       <c r="C8" s="0" t="n">
         <v>0.797</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="0" t="n">
         <v>0.02002382278442383</v>
       </c>
       <c r="E8" s="0">
@@ -19486,7 +19486,7 @@
       <c r="C9" s="0" t="n">
         <v>0.791</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="0" t="n">
         <v>0.02062098495662212</v>
       </c>
       <c r="E9" s="0">
@@ -19528,7 +19528,7 @@
       <c r="C10" s="0" t="n">
         <v>0.785</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="0" t="n">
         <v>0.02150164172053337</v>
       </c>
       <c r="E10" s="0">
@@ -19570,7 +19570,7 @@
       <c r="C11" s="0" t="n">
         <v>0.779</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="0" t="n">
         <v>0.02074512094259262</v>
       </c>
       <c r="E11" s="0">
@@ -19612,7 +19612,7 @@
       <c r="C12" s="0" t="n">
         <v>0.774</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="0" t="n">
         <v>0.02223155833780766</v>
       </c>
       <c r="E12" s="0">
@@ -19654,7 +19654,7 @@
       <c r="C13" s="0" t="n">
         <v>0.768</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="0" t="n">
         <v>0.02061885595321655</v>
       </c>
       <c r="E13" s="0">
@@ -19696,7 +19696,7 @@
       <c r="C14" s="0" t="n">
         <v>0.764</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>0.02157804369926453</v>
       </c>
       <c r="E14" s="0">
@@ -19738,7 +19738,7 @@
       <c r="C15" s="0" t="n">
         <v>0.759</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="0" t="n">
         <v>0.02084491401910782</v>
       </c>
       <c r="E15" s="0">
@@ -19780,7 +19780,7 @@
       <c r="C16" s="0" t="n">
         <v>0.754</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="0" t="n">
         <v>0.02178681455552578</v>
       </c>
       <c r="E16" s="0">
@@ -19822,7 +19822,7 @@
       <c r="C17" s="0" t="n">
         <v>0.75</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="0" t="n">
         <v>0.02149804309010506</v>
       </c>
       <c r="E17" s="0">
@@ -19864,7 +19864,7 @@
       <c r="C18" s="0" t="n">
         <v>0.746</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="0" t="n">
         <v>0.02160311862826347</v>
       </c>
       <c r="E18" s="0">
@@ -19906,7 +19906,7 @@
       <c r="C19" s="0" t="n">
         <v>0.742</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="0" t="n">
         <v>0.02212035283446312</v>
       </c>
       <c r="E19" s="0">
@@ -19948,7 +19948,7 @@
       <c r="C20" s="0" t="n">
         <v>0.737</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="0" t="n">
         <v>0.02196707017719746</v>
       </c>
       <c r="E20" s="0">
@@ -19990,7 +19990,7 @@
       <c r="C21" s="0" t="n">
         <v>0.733</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="0" t="n">
         <v>0.02210067585110664</v>
       </c>
       <c r="E21" s="0">
@@ -20032,7 +20032,7 @@
       <c r="C22" s="0" t="n">
         <v>0.729</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="0" t="n">
         <v>0.02124469913542271</v>
       </c>
       <c r="E22" s="0">
@@ -20074,7 +20074,7 @@
       <c r="C23" s="0" t="n">
         <v>0.726</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="0" t="n">
         <v>0.02223465405404568</v>
       </c>
       <c r="E23" s="0">
@@ -20116,7 +20116,7 @@
       <c r="C24" s="0" t="n">
         <v>0.722</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="0" t="n">
         <v>0.02199913933873177</v>
       </c>
       <c r="E24" s="0">
@@ -20158,7 +20158,7 @@
       <c r="C25" s="0" t="n">
         <v>0.718</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="0" t="n">
         <v>0.0226028598845005</v>
       </c>
       <c r="E25" s="0">
@@ -20200,7 +20200,7 @@
       <c r="C26" s="0" t="n">
         <v>0.714</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="0" t="n">
         <v>0.02136674337089062</v>
       </c>
       <c r="E26" s="0">
@@ -20242,7 +20242,7 @@
       <c r="C27" s="0" t="n">
         <v>0.711</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="0" t="n">
         <v>0.02244500815868378</v>
       </c>
       <c r="E27" s="0">
@@ -20284,7 +20284,7 @@
       <c r="C28" s="0" t="n">
         <v>0.707</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="0" t="n">
         <v>0.02068980224430561</v>
       </c>
       <c r="E28" s="0">
@@ -20326,7 +20326,7 @@
       <c r="C29" s="0" t="n">
         <v>0.704</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="0" t="n">
         <v>0.0218848567456007</v>
       </c>
       <c r="E29" s="0">
@@ -20368,7 +20368,7 @@
       <c r="C30" s="0" t="n">
         <v>0.701</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="0" t="n">
         <v>0.02142326533794403</v>
       </c>
       <c r="E30" s="0">
@@ -20410,7 +20410,7 @@
       <c r="C31" s="0" t="n">
         <v>0.697</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="0" t="n">
         <v>0.02206030488014221</v>
       </c>
       <c r="E31" s="0">
@@ -20452,7 +20452,7 @@
       <c r="C32" s="0" t="n">
         <v>0.694</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="0" t="n">
         <v>0.02066031657159328</v>
       </c>
       <c r="E32" s="0">
@@ -20494,7 +20494,7 @@
       <c r="C33" s="0" t="n">
         <v>0.6909999999999999</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="0" t="n">
         <v>0.02202636934816837</v>
       </c>
       <c r="E33" s="0">
@@ -20536,7 +20536,7 @@
       <c r="C34" s="0" t="n">
         <v>0.6870000000000001</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="0" t="n">
         <v>0.02086247317492962</v>
       </c>
       <c r="E34" s="0">
@@ -20578,7 +20578,7 @@
       <c r="C35" s="0" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="0" t="n">
         <v>0.02169629000127316</v>
       </c>
       <c r="E35" s="0">
@@ -20620,7 +20620,7 @@
       <c r="C36" s="0" t="n">
         <v>0.681</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="0" t="n">
         <v>0.02072627283632755</v>
       </c>
       <c r="E36" s="0">
@@ -20662,7 +20662,7 @@
       <c r="C37" s="0" t="n">
         <v>0.678</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="0" t="n">
         <v>0.02208458632230759</v>
       </c>
       <c r="E37" s="0">
@@ -20704,7 +20704,7 @@
       <c r="C38" s="0" t="n">
         <v>0.675</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="0" t="n">
         <v>0.02080466970801353</v>
       </c>
       <c r="E38" s="0">
@@ -20746,7 +20746,7 @@
       <c r="C39" s="0" t="n">
         <v>0.672</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="0" t="n">
         <v>0.02198246121406555</v>
       </c>
       <c r="E39" s="0">
@@ -20788,7 +20788,7 @@
       <c r="C40" s="0" t="n">
         <v>0.669</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="0" t="n">
         <v>0.0207621343433857</v>
       </c>
       <c r="E40" s="0">
@@ -20830,7 +20830,7 @@
       <c r="C41" s="0" t="n">
         <v>0.666</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="0" t="n">
         <v>0.02174874022603035</v>
       </c>
       <c r="E41" s="0">
@@ -20872,7 +20872,7 @@
       <c r="C42" s="0" t="n">
         <v>0.663</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.02079889923334122</v>
       </c>
       <c r="E42" s="0">
@@ -20914,7 +20914,7 @@
       <c r="C43" s="0" t="n">
         <v>0.66</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="0" t="n">
         <v>0.02128463797271252</v>
       </c>
       <c r="E43" s="0">
@@ -20956,7 +20956,7 @@
       <c r="C44" s="0" t="n">
         <v>0.657</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="0" t="n">
         <v>0.02105836756527424</v>
       </c>
       <c r="E44" s="0">
@@ -20998,7 +20998,7 @@
       <c r="C45" s="0" t="n">
         <v>0.654</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="0" t="n">
         <v>0.02128434740006924</v>
       </c>
       <c r="E45" s="0">
@@ -21040,7 +21040,7 @@
       <c r="C46" s="0" t="n">
         <v>0.651</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="0" t="n">
         <v>0.02171558514237404</v>
       </c>
       <c r="E46" s="0">
@@ -21082,7 +21082,7 @@
       <c r="C47" s="0" t="n">
         <v>0.648</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="0" t="n">
         <v>0.02162325009703636</v>
       </c>
       <c r="E47" s="0">
@@ -21124,7 +21124,7 @@
       <c r="C48" s="0" t="n">
         <v>0.646</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="0" t="n">
         <v>0.02090091444551945</v>
       </c>
       <c r="E48" s="0">
@@ -21166,7 +21166,7 @@
       <c r="C49" s="0" t="n">
         <v>0.643</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="0" t="n">
         <v>0.02139896526932716</v>
       </c>
       <c r="E49" s="0">
@@ -21208,7 +21208,7 @@
       <c r="C50" s="0" t="n">
         <v>0.64</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="0" t="n">
         <v>0.02111426182091236</v>
       </c>
       <c r="E50" s="0">
@@ -21250,7 +21250,7 @@
       <c r="C51" s="0" t="n">
         <v>0.637</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="0" t="n">
         <v>0.02089146338403225</v>
       </c>
       <c r="E51" s="0">
@@ -21292,7 +21292,7 @@
       <c r="C52" s="0" t="n">
         <v>0.634</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="0" t="n">
         <v>0.02088642492890358</v>
       </c>
       <c r="E52" s="0">
@@ -21334,7 +21334,7 @@
       <c r="C53" s="0" t="n">
         <v>0.631</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="0" t="n">
         <v>0.02163968607783318</v>
       </c>
       <c r="E53" s="0">
@@ -21376,7 +21376,7 @@
       <c r="C54" s="0" t="n">
         <v>0.629</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="0" t="n">
         <v>0.0208536833524704</v>
       </c>
       <c r="E54" s="0">
@@ -21418,7 +21418,7 @@
       <c r="C55" s="0" t="n">
         <v>0.626</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="0" t="n">
         <v>0.02042403817176819</v>
       </c>
       <c r="E55" s="0">
@@ -21460,7 +21460,7 @@
       <c r="C56" s="0" t="n">
         <v>0.623</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="0" t="n">
         <v>0.02127382904291153</v>
       </c>
       <c r="E56" s="0">
@@ -21502,7 +21502,7 @@
       <c r="C57" s="0" t="n">
         <v>0.621</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="0" t="n">
         <v>0.02156965248286724</v>
       </c>
       <c r="E57" s="0">
@@ -21544,7 +21544,7 @@
       <c r="C58" s="0" t="n">
         <v>0.618</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="0" t="n">
         <v>0.0206918828189373</v>
       </c>
       <c r="E58" s="0">
@@ -21586,7 +21586,7 @@
       <c r="C59" s="0" t="n">
         <v>0.615</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="0" t="n">
         <v>0.02107076346874237</v>
       </c>
       <c r="E59" s="0">
@@ -21628,7 +21628,7 @@
       <c r="C60" s="0" t="n">
         <v>0.613</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="0" t="n">
         <v>0.02087909355759621</v>
       </c>
       <c r="E60" s="0">
@@ -21670,7 +21670,7 @@
       <c r="C61" s="0" t="n">
         <v>0.61</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="0" t="n">
         <v>0.02139941975474358</v>
       </c>
       <c r="E61" s="0">
@@ -21712,7 +21712,7 @@
       <c r="C62" s="0" t="n">
         <v>0.608</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="0" t="n">
         <v>0.02168705686926842</v>
       </c>
       <c r="E62" s="0">
@@ -21754,7 +21754,7 @@
       <c r="C63" s="0" t="n">
         <v>0.605</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="0" t="n">
         <v>0.02088871784508228</v>
       </c>
       <c r="E63" s="0">
@@ -21796,7 +21796,7 @@
       <c r="C64" s="0" t="n">
         <v>0.603</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="0" t="n">
         <v>0.02038130722939968</v>
       </c>
       <c r="E64" s="0">
@@ -21838,7 +21838,7 @@
       <c r="C65" s="0" t="n">
         <v>0.6</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="0" t="n">
         <v>0.02090147696435452</v>
       </c>
       <c r="E65" s="0">
@@ -21880,7 +21880,7 @@
       <c r="C66" s="0" t="n">
         <v>0.597</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="0" t="n">
         <v>0.02089935913681984</v>
       </c>
       <c r="E66" s="0">
@@ -21922,7 +21922,7 @@
       <c r="C67" s="0" t="n">
         <v>0.595</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="0" t="n">
         <v>0.02123693376779556</v>
       </c>
       <c r="E67" s="0">
@@ -21964,7 +21964,7 @@
       <c r="C68" s="0" t="n">
         <v>0.592</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="0" t="n">
         <v>0.02121633850038052</v>
       </c>
       <c r="E68" s="0">
@@ -22006,7 +22006,7 @@
       <c r="C69" s="0" t="n">
         <v>0.59</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="0" t="n">
         <v>0.02192088775336742</v>
       </c>
       <c r="E69" s="0">
@@ -22048,7 +22048,7 @@
       <c r="C70" s="0" t="n">
         <v>0.587</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="0" t="n">
         <v>0.02134180627763271</v>
       </c>
       <c r="E70" s="0">
@@ -22090,7 +22090,7 @@
       <c r="C71" s="0" t="n">
         <v>0.585</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="0" t="n">
         <v>0.02118257060647011</v>
       </c>
       <c r="E71" s="0">
@@ -22132,7 +22132,7 @@
       <c r="C72" s="0" t="n">
         <v>0.582</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="0" t="n">
         <v>0.02070923149585724</v>
       </c>
       <c r="E72" s="0">
@@ -22174,7 +22174,7 @@
       <c r="C73" s="0" t="n">
         <v>0.58</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="0" t="n">
         <v>0.02084982767701149</v>
       </c>
       <c r="E73" s="0">
@@ -22216,7 +22216,7 @@
       <c r="C74" s="0" t="n">
         <v>0.578</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="0" t="n">
         <v>0.02178002707660198</v>
       </c>
       <c r="E74" s="0">
@@ -22258,7 +22258,7 @@
       <c r="C75" s="0" t="n">
         <v>0.575</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="0" t="n">
         <v>0.0216306746006012</v>
       </c>
       <c r="E75" s="0">
@@ -22300,7 +22300,7 @@
       <c r="C76" s="0" t="n">
         <v>0.573</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="0" t="n">
         <v>0.0215228870511055</v>
       </c>
       <c r="E76" s="0">
@@ -22342,7 +22342,7 @@
       <c r="C77" s="0" t="n">
         <v>0.57</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="0" t="n">
         <v>0.02099636942148209</v>
       </c>
       <c r="E77" s="0">
@@ -22384,7 +22384,7 @@
       <c r="C78" s="0" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="0" t="n">
         <v>0.02120652794837952</v>
       </c>
       <c r="E78" s="0">
@@ -22426,7 +22426,7 @@
       <c r="C79" s="0" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="0" t="n">
         <v>0.02128704264760017</v>
       </c>
       <c r="E79" s="0">
@@ -22468,7 +22468,7 @@
       <c r="C80" s="0" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="0" t="n">
         <v>0.0215698704123497</v>
       </c>
       <c r="E80" s="0">
@@ -22510,7 +22510,7 @@
       <c r="C81" s="0" t="n">
         <v>0.5610000000000001</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="0" t="n">
         <v>0.02135146409273148</v>
       </c>
       <c r="E81" s="0">
@@ -22552,7 +22552,7 @@
       <c r="C82" s="0" t="n">
         <v>0.5580000000000001</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="0" t="n">
         <v>0.02219929546117783</v>
       </c>
       <c r="E82" s="0">
@@ -22594,7 +22594,7 @@
       <c r="C83" s="0" t="n">
         <v>0.556</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="0" t="n">
         <v>0.02134930714964867</v>
       </c>
       <c r="E83" s="0">
@@ -22636,7 +22636,7 @@
       <c r="C84" s="0" t="n">
         <v>0.554</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="0" t="n">
         <v>0.0212129782885313</v>
       </c>
       <c r="E84" s="0">
@@ -22678,7 +22678,7 @@
       <c r="C85" s="0" t="n">
         <v>0.551</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="0" t="n">
         <v>0.02233623340725899</v>
       </c>
       <c r="E85" s="0">
@@ -22720,7 +22720,7 @@
       <c r="C86" s="0" t="n">
         <v>0.549</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="0" t="n">
         <v>0.0209533553570509</v>
       </c>
       <c r="E86" s="0">
@@ -22762,7 +22762,7 @@
       <c r="C87" s="0" t="n">
         <v>0.546</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="0" t="n">
         <v>0.02204925194382668</v>
       </c>
       <c r="E87" s="0">
@@ -22804,7 +22804,7 @@
       <c r="C88" s="0" t="n">
         <v>0.544</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="0" t="n">
         <v>0.02171573415398598</v>
       </c>
       <c r="E88" s="0">
@@ -22846,7 +22846,7 @@
       <c r="C89" s="0" t="n">
         <v>0.542</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="0" t="n">
         <v>0.0216961745172739</v>
       </c>
       <c r="E89" s="0">
@@ -22888,7 +22888,7 @@
       <c r="C90" s="0" t="n">
         <v>0.539</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="0" t="n">
         <v>0.02190676517784595</v>
       </c>
       <c r="E90" s="0">
@@ -22930,7 +22930,7 @@
       <c r="C91" s="0" t="n">
         <v>0.537</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="0" t="n">
         <v>0.02175609022378922</v>
       </c>
       <c r="E91" s="0">
@@ -22972,7 +22972,7 @@
       <c r="C92" s="0" t="n">
         <v>0.534</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="0" t="n">
         <v>0.02242948859930038</v>
       </c>
       <c r="E92" s="0">
@@ -23014,7 +23014,7 @@
       <c r="C93" s="0" t="n">
         <v>0.533</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="0" t="n">
         <v>0.0215414147824049</v>
       </c>
       <c r="E93" s="0">
@@ -23056,7 +23056,7 @@
       <c r="C94" s="0" t="n">
         <v>0.53</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="0" t="n">
         <v>0.02252337895333767</v>
       </c>
       <c r="E94" s="0">
@@ -23098,7 +23098,7 @@
       <c r="C95" s="0" t="n">
         <v>0.528</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="0" t="n">
         <v>0.02160502783954144</v>
       </c>
       <c r="E95" s="0">
@@ -23140,7 +23140,7 @@
       <c r="C96" s="0" t="n">
         <v>0.526</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.02235906384885311</v>
       </c>
       <c r="E96" s="0">
@@ -23182,7 +23182,7 @@
       <c r="C97" s="0" t="n">
         <v>0.524</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="0" t="n">
         <v>0.0217084027826786</v>
       </c>
       <c r="E97" s="0">
@@ -23224,7 +23224,7 @@
       <c r="C98" s="0" t="n">
         <v>0.521</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="0" t="n">
         <v>0.02225402183830738</v>
       </c>
       <c r="E98" s="0">
@@ -23266,7 +23266,7 @@
       <c r="C99" s="0" t="n">
         <v>0.519</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="0" t="n">
         <v>0.02203675732016563</v>
       </c>
       <c r="E99" s="0">
@@ -23308,7 +23308,7 @@
       <c r="C100" s="0" t="n">
         <v>0.517</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="0" t="n">
         <v>0.02238716930150986</v>
       </c>
       <c r="E100" s="0">
@@ -23350,7 +23350,7 @@
       <c r="C101" s="0" t="n">
         <v>0.514</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="0" t="n">
         <v>0.02200327999889851</v>
       </c>
       <c r="E101" s="0">
@@ -23392,7 +23392,7 @@
       <c r="C102" s="0" t="n">
         <v>0.512</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="0" t="n">
         <v>0.02229078486561775</v>
       </c>
       <c r="E102" s="0">
@@ -23434,7 +23434,7 @@
       <c r="C103" s="0" t="n">
         <v>0.51</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="0" t="n">
         <v>0.02204912714660168</v>
       </c>
       <c r="E103" s="0">
@@ -23476,7 +23476,7 @@
       <c r="C104" s="0" t="n">
         <v>0.508</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="0" t="n">
         <v>0.02202761545777321</v>
       </c>
       <c r="E104" s="0">
@@ -23518,7 +23518,7 @@
       <c r="C105" s="0" t="n">
         <v>0.506</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="0" t="n">
         <v>0.02176796086132526</v>
       </c>
       <c r="E105" s="0">
@@ -23560,7 +23560,7 @@
       <c r="C106" s="0" t="n">
         <v>0.503</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="0" t="n">
         <v>0.02218662574887276</v>
       </c>
       <c r="E106" s="0">
@@ -23602,7 +23602,7 @@
       <c r="C107" s="0" t="n">
         <v>0.501</v>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="0" t="n">
         <v>0.02234361320734024</v>
       </c>
       <c r="E107" s="0">
@@ -23644,7 +23644,7 @@
       <c r="C108" s="0" t="n">
         <v>0.499</v>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="0" t="n">
         <v>0.02194085530936718</v>
       </c>
       <c r="E108" s="0">
@@ -23686,7 +23686,7 @@
       <c r="C109" s="0" t="n">
         <v>0.496</v>
       </c>
-      <c r="D109" t="n">
+      <c r="D109" s="0" t="n">
         <v>0.02266308106482029</v>
       </c>
       <c r="E109" s="0">
@@ -23728,7 +23728,7 @@
       <c r="C110" s="0" t="n">
         <v>0.494</v>
       </c>
-      <c r="D110" t="n">
+      <c r="D110" s="0" t="n">
         <v>0.02264226041734219</v>
       </c>
       <c r="E110" s="0">
@@ -23770,7 +23770,7 @@
       <c r="C111" s="0" t="n">
         <v>0.492</v>
       </c>
-      <c r="D111" t="n">
+      <c r="D111" s="0" t="n">
         <v>0.02145604602992535</v>
       </c>
       <c r="E111" s="0">
@@ -23812,7 +23812,7 @@
       <c r="C112" s="0" t="n">
         <v>0.49</v>
       </c>
-      <c r="D112" t="n">
+      <c r="D112" s="0" t="n">
         <v>0.02272169478237629</v>
       </c>
       <c r="E112" s="0">
@@ -23854,7 +23854,7 @@
       <c r="C113" s="0" t="n">
         <v>0.488</v>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.02283627167344093</v>
       </c>
       <c r="E113" s="0">
@@ -23896,7 +23896,7 @@
       <c r="C114" s="0" t="n">
         <v>0.485</v>
       </c>
-      <c r="D114" t="n">
+      <c r="D114" s="0" t="n">
         <v>0.02256097830832005</v>
       </c>
       <c r="E114" s="0">
@@ -23938,7 +23938,7 @@
       <c r="C115" s="0" t="n">
         <v>0.483</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D115" s="0" t="n">
         <v>0.02283190004527569</v>
       </c>
       <c r="E115" s="0">
@@ -23980,7 +23980,7 @@
       <c r="C116" s="0" t="n">
         <v>0.481</v>
       </c>
-      <c r="D116" t="n">
+      <c r="D116" s="0" t="n">
         <v>0.02224512957036495</v>
       </c>
       <c r="E116" s="0">
@@ -24022,7 +24022,7 @@
       <c r="C117" s="0" t="n">
         <v>0.479</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D117" s="0" t="n">
         <v>0.02277129143476486</v>
       </c>
       <c r="E117" s="0">
@@ -24064,7 +24064,7 @@
       <c r="C118" s="0" t="n">
         <v>0.477</v>
       </c>
-      <c r="D118" t="n">
+      <c r="D118" s="0" t="n">
         <v>0.02282169088721275</v>
       </c>
       <c r="E118" s="0">
@@ -24106,7 +24106,7 @@
       <c r="C119" s="0" t="n">
         <v>0.474</v>
       </c>
-      <c r="D119" t="n">
+      <c r="D119" s="0" t="n">
         <v>0.02233251929283142</v>
       </c>
       <c r="E119" s="0">
@@ -24148,7 +24148,7 @@
       <c r="C120" s="0" t="n">
         <v>0.473</v>
       </c>
-      <c r="D120" t="n">
+      <c r="D120" s="0" t="n">
         <v>0.02308384887874126</v>
       </c>
       <c r="E120" s="0">
@@ -24190,7 +24190,7 @@
       <c r="C121" s="0" t="n">
         <v>0.47</v>
       </c>
-      <c r="D121" t="n">
+      <c r="D121" s="0" t="n">
         <v>0.02248584665358067</v>
       </c>
       <c r="E121" s="0">
@@ -24232,7 +24232,7 @@
       <c r="C122" s="0" t="n">
         <v>0.468</v>
       </c>
-      <c r="D122" t="n">
+      <c r="D122" s="0" t="n">
         <v>0.02315918728709221</v>
       </c>
       <c r="E122" s="0">
@@ -24274,7 +24274,7 @@
       <c r="C123" s="0" t="n">
         <v>0.466</v>
       </c>
-      <c r="D123" t="n">
+      <c r="D123" s="0" t="n">
         <v>0.02308138087391853</v>
       </c>
       <c r="E123" s="0">
@@ -24316,7 +24316,7 @@
       <c r="C124" s="0" t="n">
         <v>0.464</v>
       </c>
-      <c r="D124" t="n">
+      <c r="D124" s="0" t="n">
         <v>0.02228741347789764</v>
       </c>
       <c r="E124" s="0">
@@ -24358,7 +24358,7 @@
       <c r="C125" s="0" t="n">
         <v>0.462</v>
       </c>
-      <c r="D125" t="n">
+      <c r="D125" s="0" t="n">
         <v>0.02303110808134079</v>
       </c>
       <c r="E125" s="0">
@@ -24400,7 +24400,7 @@
       <c r="C126" s="0" t="n">
         <v>0.46</v>
       </c>
-      <c r="D126" t="n">
+      <c r="D126" s="0" t="n">
         <v>0.02348831482231617</v>
       </c>
       <c r="E126" s="0">
@@ -24442,7 +24442,7 @@
       <c r="C127" s="0" t="n">
         <v>0.458</v>
       </c>
-      <c r="D127" t="n">
+      <c r="D127" s="0" t="n">
         <v>0.02262923307716846</v>
       </c>
       <c r="E127" s="0">
@@ -24484,7 +24484,7 @@
       <c r="C128" s="0" t="n">
         <v>0.455</v>
       </c>
-      <c r="D128" t="n">
+      <c r="D128" s="0" t="n">
         <v>0.02375646680593491</v>
       </c>
       <c r="E128" s="0">
@@ -24526,7 +24526,7 @@
       <c r="C129" s="0" t="n">
         <v>0.453</v>
       </c>
-      <c r="D129" t="n">
+      <c r="D129" s="0" t="n">
         <v>0.02298040315508842</v>
       </c>
       <c r="E129" s="0">
@@ -24568,7 +24568,7 @@
       <c r="C130" s="0" t="n">
         <v>0.451</v>
       </c>
-      <c r="D130" t="n">
+      <c r="D130" s="0" t="n">
         <v>0.0228426568210125</v>
       </c>
       <c r="E130" s="0">
@@ -24610,7 +24610,7 @@
       <c r="C131" s="0" t="n">
         <v>0.449</v>
       </c>
-      <c r="D131" t="n">
+      <c r="D131" s="0" t="n">
         <v>0.02334821410477161</v>
       </c>
       <c r="E131" s="0">
@@ -24652,7 +24652,7 @@
       <c r="C132" s="0" t="n">
         <v>0.447</v>
       </c>
-      <c r="D132" t="n">
+      <c r="D132" s="0" t="n">
         <v>0.02255835197865963</v>
       </c>
       <c r="E132" s="0">
@@ -24694,7 +24694,7 @@
       <c r="C133" s="0" t="n">
         <v>0.445</v>
       </c>
-      <c r="D133" t="n">
+      <c r="D133" s="0" t="n">
         <v>0.02312240190804005</v>
       </c>
       <c r="E133" s="0">
@@ -24736,7 +24736,7 @@
       <c r="C134" s="0" t="n">
         <v>0.443</v>
       </c>
-      <c r="D134" t="n">
+      <c r="D134" s="0" t="n">
         <v>0.02291266620159149</v>
       </c>
       <c r="E134" s="0">
@@ -24778,7 +24778,7 @@
       <c r="C135" s="0" t="n">
         <v>0.441</v>
       </c>
-      <c r="D135" t="n">
+      <c r="D135" s="0" t="n">
         <v>0.023176034912467</v>
       </c>
       <c r="E135" s="0">
@@ -24820,7 +24820,7 @@
       <c r="C136" s="0" t="n">
         <v>0.439</v>
       </c>
-      <c r="D136" t="n">
+      <c r="D136" s="0" t="n">
         <v>0.02292532101273537</v>
       </c>
       <c r="E136" s="0">
@@ -24862,7 +24862,7 @@
       <c r="C137" s="0" t="n">
         <v>0.437</v>
       </c>
-      <c r="D137" t="n">
+      <c r="D137" s="0" t="n">
         <v>0.02327945083379745</v>
       </c>
       <c r="E137" s="0">
@@ -24904,7 +24904,7 @@
       <c r="C138" s="0" t="n">
         <v>0.434</v>
       </c>
-      <c r="D138" t="n">
+      <c r="D138" s="0" t="n">
         <v>0.02313651889562607</v>
       </c>
       <c r="E138" s="0">
@@ -24946,7 +24946,7 @@
       <c r="C139" s="0" t="n">
         <v>0.432</v>
       </c>
-      <c r="D139" t="n">
+      <c r="D139" s="0" t="n">
         <v>0.02359609119594097</v>
       </c>
       <c r="E139" s="0">
@@ -24988,7 +24988,7 @@
       <c r="C140" s="0" t="n">
         <v>0.43</v>
       </c>
-      <c r="D140" t="n">
+      <c r="D140" s="0" t="n">
         <v>0.02316553890705109</v>
       </c>
       <c r="E140" s="0">
@@ -25030,7 +25030,7 @@
       <c r="C141" s="0" t="n">
         <v>0.428</v>
       </c>
-      <c r="D141" t="n">
+      <c r="D141" s="0" t="n">
         <v>0.02403800003230572</v>
       </c>
       <c r="E141" s="0">
@@ -25072,7 +25072,7 @@
       <c r="C142" s="0" t="n">
         <v>0.426</v>
       </c>
-      <c r="D142" t="n">
+      <c r="D142" s="0" t="n">
         <v>0.0228748694062233</v>
       </c>
       <c r="E142" s="0">
@@ -25114,7 +25114,7 @@
       <c r="C143" s="0" t="n">
         <v>0.424</v>
       </c>
-      <c r="D143" t="n">
+      <c r="D143" s="0" t="n">
         <v>0.02321753092110157</v>
       </c>
       <c r="E143" s="0">
@@ -25156,7 +25156,7 @@
       <c r="C144" s="0" t="n">
         <v>0.422</v>
       </c>
-      <c r="D144" t="n">
+      <c r="D144" s="0" t="n">
         <v>0.02334983088076115</v>
       </c>
       <c r="E144" s="0">
@@ -25198,7 +25198,7 @@
       <c r="C145" s="0" t="n">
         <v>0.42</v>
       </c>
-      <c r="D145" t="n">
+      <c r="D145" s="0" t="n">
         <v>0.02308961376547813</v>
       </c>
       <c r="E145" s="0">
@@ -25240,7 +25240,7 @@
       <c r="C146" s="0" t="n">
         <v>0.418</v>
       </c>
-      <c r="D146" t="n">
+      <c r="D146" s="0" t="n">
         <v>0.02444537356495857</v>
       </c>
       <c r="E146" s="0">
@@ -25282,7 +25282,7 @@
       <c r="C147" s="0" t="n">
         <v>0.416</v>
       </c>
-      <c r="D147" t="n">
+      <c r="D147" s="0" t="n">
         <v>0.02307135425508022</v>
       </c>
       <c r="E147" s="0">
@@ -25324,7 +25324,7 @@
       <c r="C148" s="0" t="n">
         <v>0.413</v>
       </c>
-      <c r="D148" t="n">
+      <c r="D148" s="0" t="n">
         <v>0.02379290014505386</v>
       </c>
       <c r="E148" s="0">
@@ -25366,7 +25366,7 @@
       <c r="C149" s="0" t="n">
         <v>0.411</v>
       </c>
-      <c r="D149" t="n">
+      <c r="D149" s="0" t="n">
         <v>0.02341685071587563</v>
       </c>
       <c r="E149" s="0">
@@ -25408,7 +25408,7 @@
       <c r="C150" s="0" t="n">
         <v>0.409</v>
       </c>
-      <c r="D150" t="n">
+      <c r="D150" s="0" t="n">
         <v>0.02343933098018169</v>
       </c>
       <c r="E150" s="0">
@@ -25450,7 +25450,7 @@
       <c r="C151" s="0" t="n">
         <v>0.407</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D151" s="0" t="n">
         <v>0.02361765690147877</v>
       </c>
       <c r="E151" s="0">
@@ -25492,7 +25492,7 @@
       <c r="C152" s="0" t="n">
         <v>0.405</v>
       </c>
-      <c r="D152" t="n">
+      <c r="D152" s="0" t="n">
         <v>0.02412284165620804</v>
       </c>
       <c r="E152" s="0">
@@ -25534,7 +25534,7 @@
       <c r="C153" s="0" t="n">
         <v>0.403</v>
       </c>
-      <c r="D153" t="n">
+      <c r="D153" s="0" t="n">
         <v>0.02367998659610748</v>
       </c>
       <c r="E153" s="0">
@@ -25576,7 +25576,7 @@
       <c r="C154" s="0" t="n">
         <v>0.401</v>
       </c>
-      <c r="D154" t="n">
+      <c r="D154" s="0" t="n">
         <v>0.02378236874938011</v>
       </c>
       <c r="E154" s="0">
@@ -25618,7 +25618,7 @@
       <c r="C155" s="0" t="n">
         <v>0.399</v>
       </c>
-      <c r="D155" t="n">
+      <c r="D155" s="0" t="n">
         <v>0.02381190285086632</v>
       </c>
       <c r="E155" s="0">
@@ -25660,7 +25660,7 @@
       <c r="C156" s="0" t="n">
         <v>0.397</v>
       </c>
-      <c r="D156" t="n">
+      <c r="D156" s="0" t="n">
         <v>0.02335663884878159</v>
       </c>
       <c r="E156" s="0">
@@ -25702,7 +25702,7 @@
       <c r="C157" s="0" t="n">
         <v>0.395</v>
       </c>
-      <c r="D157" t="n">
+      <c r="D157" s="0" t="n">
         <v>0.02376625686883926</v>
       </c>
       <c r="E157" s="0">
@@ -25744,7 +25744,7 @@
       <c r="C158" s="0" t="n">
         <v>0.393</v>
       </c>
-      <c r="D158" t="n">
+      <c r="D158" s="0" t="n">
         <v>0.02348150312900543</v>
       </c>
       <c r="E158" s="0">
@@ -25786,7 +25786,7 @@
       <c r="C159" s="0" t="n">
         <v>0.39</v>
       </c>
-      <c r="D159" t="n">
+      <c r="D159" s="0" t="n">
         <v>0.02421257458627224</v>
       </c>
       <c r="E159" s="0">
@@ -25828,7 +25828,7 @@
       <c r="C160" s="0" t="n">
         <v>0.388</v>
       </c>
-      <c r="D160" t="n">
+      <c r="D160" s="0" t="n">
         <v>0.02338164113461971</v>
       </c>
       <c r="E160" s="0">
@@ -25870,7 +25870,7 @@
       <c r="C161" s="0" t="n">
         <v>0.386</v>
       </c>
-      <c r="D161" t="n">
+      <c r="D161" s="0" t="n">
         <v>0.02417968027293682</v>
       </c>
       <c r="E161" s="0">
@@ -25912,7 +25912,7 @@
       <c r="C162" s="0" t="n">
         <v>0.384</v>
       </c>
-      <c r="D162" t="n">
+      <c r="D162" s="0" t="n">
         <v>0.02359800599515438</v>
       </c>
       <c r="E162" s="0">
@@ -25954,7 +25954,7 @@
       <c r="C163" s="0" t="n">
         <v>0.382</v>
       </c>
-      <c r="D163" t="n">
+      <c r="D163" s="0" t="n">
         <v>0.02405710332095623</v>
       </c>
       <c r="E163" s="0">
@@ -25996,7 +25996,7 @@
       <c r="C164" s="0" t="n">
         <v>0.38</v>
       </c>
-      <c r="D164" t="n">
+      <c r="D164" s="0" t="n">
         <v>0.02362007275223732</v>
       </c>
       <c r="E164" s="0">
@@ -26038,7 +26038,7 @@
       <c r="C165" s="0" t="n">
         <v>0.378</v>
       </c>
-      <c r="D165" t="n">
+      <c r="D165" s="0" t="n">
         <v>0.02441132627427578</v>
       </c>
       <c r="E165" s="0">
@@ -26080,7 +26080,7 @@
       <c r="C166" s="0" t="n">
         <v>0.375</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D166" s="0" t="n">
         <v>0.02377547696232796</v>
       </c>
       <c r="E166" s="0">
@@ -26122,7 +26122,7 @@
       <c r="C167" s="0" t="n">
         <v>0.373</v>
       </c>
-      <c r="D167" t="n">
+      <c r="D167" s="0" t="n">
         <v>0.02424614503979683</v>
       </c>
       <c r="E167" s="0">
@@ -26164,7 +26164,7 @@
       <c r="C168" s="0" t="n">
         <v>0.371</v>
       </c>
-      <c r="D168" t="n">
+      <c r="D168" s="0" t="n">
         <v>0.02394500561058521</v>
       </c>
       <c r="E168" s="0">
@@ -26206,7 +26206,7 @@
       <c r="C169" s="0" t="n">
         <v>0.369</v>
       </c>
-      <c r="D169" t="n">
+      <c r="D169" s="0" t="n">
         <v>0.02406875789165497</v>
       </c>
       <c r="E169" s="0">
@@ -26248,7 +26248,7 @@
       <c r="C170" s="0" t="n">
         <v>0.367</v>
       </c>
-      <c r="D170" t="n">
+      <c r="D170" s="0" t="n">
         <v>0.02440095134079456</v>
       </c>
       <c r="E170" s="0">
@@ -26290,7 +26290,7 @@
       <c r="C171" s="0" t="n">
         <v>0.365</v>
       </c>
-      <c r="D171" t="n">
+      <c r="D171" s="0" t="n">
         <v>0.02434027567505836</v>
       </c>
       <c r="E171" s="0">
@@ -26332,7 +26332,7 @@
       <c r="C172" s="0" t="n">
         <v>0.362</v>
       </c>
-      <c r="D172" t="n">
+      <c r="D172" s="0" t="n">
         <v>0.02376594208180904</v>
       </c>
       <c r="E172" s="0">
@@ -26374,7 +26374,7 @@
       <c r="C173" s="0" t="n">
         <v>0.361</v>
       </c>
-      <c r="D173" t="n">
+      <c r="D173" s="0" t="n">
         <v>0.02431243099272251</v>
       </c>
       <c r="E173" s="0">
@@ -26416,7 +26416,7 @@
       <c r="C174" s="0" t="n">
         <v>0.358</v>
       </c>
-      <c r="D174" t="n">
+      <c r="D174" s="0" t="n">
         <v>0.02424491569399834</v>
       </c>
       <c r="E174" s="0">
@@ -26458,7 +26458,7 @@
       <c r="C175" s="0" t="n">
         <v>0.356</v>
       </c>
-      <c r="D175" t="n">
+      <c r="D175" s="0" t="n">
         <v>0.02432944253087044</v>
       </c>
       <c r="E175" s="0">
@@ -26500,7 +26500,7 @@
       <c r="C176" s="0" t="n">
         <v>0.354</v>
       </c>
-      <c r="D176" t="n">
+      <c r="D176" s="0" t="n">
         <v>0.02473657205700874</v>
       </c>
       <c r="E176" s="0">
@@ -26542,7 +26542,7 @@
       <c r="C177" s="0" t="n">
         <v>0.352</v>
       </c>
-      <c r="D177" t="n">
+      <c r="D177" s="0" t="n">
         <v>0.02427547425031662</v>
       </c>
       <c r="E177" s="0">
@@ -26584,7 +26584,7 @@
       <c r="C178" s="0" t="n">
         <v>0.35</v>
       </c>
-      <c r="D178" t="n">
+      <c r="D178" s="0" t="n">
         <v>0.02418882772326469</v>
       </c>
       <c r="E178" s="0">
@@ -26626,7 +26626,7 @@
       <c r="C179" s="0" t="n">
         <v>0.348</v>
       </c>
-      <c r="D179" t="n">
+      <c r="D179" s="0" t="n">
         <v>0.0245915874838829</v>
       </c>
       <c r="E179" s="0">
@@ -26668,7 +26668,7 @@
       <c r="C180" s="0" t="n">
         <v>0.346</v>
       </c>
-      <c r="D180" t="n">
+      <c r="D180" s="0" t="n">
         <v>0.02487228251993656</v>
       </c>
       <c r="E180" s="0">
@@ -26710,7 +26710,7 @@
       <c r="C181" s="0" t="n">
         <v>0.343</v>
       </c>
-      <c r="D181" t="n">
+      <c r="D181" s="0" t="n">
         <v>0.02499474212527275</v>
       </c>
       <c r="E181" s="0">
@@ -26752,7 +26752,7 @@
       <c r="C182" s="0" t="n">
         <v>0.341</v>
       </c>
-      <c r="D182" t="n">
+      <c r="D182" s="0" t="n">
         <v>0.02505173347890377</v>
       </c>
       <c r="E182" s="0">
@@ -26794,7 +26794,7 @@
       <c r="C183" s="0" t="n">
         <v>0.339</v>
       </c>
-      <c r="D183" t="n">
+      <c r="D183" s="0" t="n">
         <v>0.02456580474972725</v>
       </c>
       <c r="E183" s="0">
@@ -26836,7 +26836,7 @@
       <c r="C184" s="0" t="n">
         <v>0.337</v>
       </c>
-      <c r="D184" t="n">
+      <c r="D184" s="0" t="n">
         <v>0.02429625019431114</v>
       </c>
       <c r="E184" s="0">
@@ -26878,7 +26878,7 @@
       <c r="C185" s="0" t="n">
         <v>0.335</v>
       </c>
-      <c r="D185" t="n">
+      <c r="D185" s="0" t="n">
         <v>0.02401648834347725</v>
       </c>
       <c r="E185" s="0">
@@ -26920,7 +26920,7 @@
       <c r="C186" s="0" t="n">
         <v>0.333</v>
       </c>
-      <c r="D186" t="n">
+      <c r="D186" s="0" t="n">
         <v>0.0249500460922718</v>
       </c>
       <c r="E186" s="0">
@@ -26962,7 +26962,7 @@
       <c r="C187" s="0" t="n">
         <v>0.33</v>
       </c>
-      <c r="D187" t="n">
+      <c r="D187" s="0" t="n">
         <v>0.02474693581461906</v>
       </c>
       <c r="E187" s="0">
@@ -27004,7 +27004,7 @@
       <c r="C188" s="0" t="n">
         <v>0.328</v>
       </c>
-      <c r="D188" t="n">
+      <c r="D188" s="0" t="n">
         <v>0.0247977115213871</v>
       </c>
       <c r="E188" s="0">
@@ -27046,7 +27046,7 @@
       <c r="C189" s="0" t="n">
         <v>0.327</v>
       </c>
-      <c r="D189" t="n">
+      <c r="D189" s="0" t="n">
         <v>0.02455391362309456</v>
       </c>
       <c r="E189" s="0">
@@ -27088,7 +27088,7 @@
       <c r="C190" s="0" t="n">
         <v>0.324</v>
       </c>
-      <c r="D190" t="n">
+      <c r="D190" s="0" t="n">
         <v>0.02486999705433846</v>
       </c>
       <c r="E190" s="0">
@@ -27130,7 +27130,7 @@
       <c r="C191" s="0" t="n">
         <v>0.322</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D191" s="0" t="n">
         <v>0.02434824593365192</v>
       </c>
       <c r="E191" s="0">
@@ -27172,7 +27172,7 @@
       <c r="C192" s="0" t="n">
         <v>0.32</v>
       </c>
-      <c r="D192" t="n">
+      <c r="D192" s="0" t="n">
         <v>0.02544496022164822</v>
       </c>
       <c r="E192" s="0">
@@ -27214,7 +27214,7 @@
       <c r="C193" s="0" t="n">
         <v>0.317</v>
       </c>
-      <c r="D193" t="n">
+      <c r="D193" s="0" t="n">
         <v>0.02464304119348526</v>
       </c>
       <c r="E193" s="0">
@@ -27256,7 +27256,7 @@
       <c r="C194" s="0" t="n">
         <v>0.315</v>
       </c>
-      <c r="D194" t="n">
+      <c r="D194" s="0" t="n">
         <v>0.02476061508059502</v>
       </c>
       <c r="E194" s="0">
@@ -27298,7 +27298,7 @@
       <c r="C195" s="0" t="n">
         <v>0.313</v>
       </c>
-      <c r="D195" t="n">
+      <c r="D195" s="0" t="n">
         <v>0.02476061508059502</v>
       </c>
       <c r="E195" s="0">
@@ -27340,7 +27340,7 @@
       <c r="C196" s="0" t="n">
         <v>0.311</v>
       </c>
-      <c r="D196" t="n">
+      <c r="D196" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E196" s="0">
@@ -27381,7 +27381,7 @@
       <c r="C197" s="0" t="n">
         <v>0.309</v>
       </c>
-      <c r="D197" t="n">
+      <c r="D197" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E197" s="0">
@@ -27422,7 +27422,7 @@
       <c r="C198" s="0" t="n">
         <v>0.306</v>
       </c>
-      <c r="D198" t="n">
+      <c r="D198" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E198" s="0">
@@ -27463,7 +27463,7 @@
       <c r="C199" s="0" t="n">
         <v>0.304</v>
       </c>
-      <c r="D199" t="n">
+      <c r="D199" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E199" s="0">
@@ -27504,7 +27504,7 @@
       <c r="C200" s="0" t="n">
         <v>0.301</v>
       </c>
-      <c r="D200" t="n">
+      <c r="D200" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E200" s="0">
@@ -27545,7 +27545,7 @@
       <c r="C201" s="0" t="n">
         <v>0.299</v>
       </c>
-      <c r="D201" t="n">
+      <c r="D201" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E201" s="0">
@@ -27586,7 +27586,7 @@
       <c r="C202" s="0" t="n">
         <v>0.297</v>
       </c>
-      <c r="D202" t="n">
+      <c r="D202" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E202" s="0">
@@ -27627,7 +27627,7 @@
       <c r="C203" s="0" t="n">
         <v>0.295</v>
       </c>
-      <c r="D203" t="n">
+      <c r="D203" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E203" s="0">
@@ -27668,7 +27668,7 @@
       <c r="C204" s="0" t="n">
         <v>0.293</v>
       </c>
-      <c r="D204" t="n">
+      <c r="D204" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E204" s="0">
@@ -27709,7 +27709,7 @@
       <c r="C205" s="0" t="n">
         <v>0.291</v>
       </c>
-      <c r="D205" t="n">
+      <c r="D205" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E205" s="0">
@@ -27750,7 +27750,7 @@
       <c r="C206" s="0" t="n">
         <v>0.288</v>
       </c>
-      <c r="D206" t="n">
+      <c r="D206" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E206" s="0">
@@ -27791,7 +27791,7 @@
       <c r="C207" s="0" t="n">
         <v>0.286</v>
       </c>
-      <c r="D207" t="n">
+      <c r="D207" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E207" s="0">
@@ -27832,7 +27832,7 @@
       <c r="C208" s="0" t="n">
         <v>0.284</v>
       </c>
-      <c r="D208" t="n">
+      <c r="D208" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E208" s="0">
@@ -27873,7 +27873,7 @@
       <c r="C209" s="0" t="n">
         <v>0.282</v>
       </c>
-      <c r="D209" t="n">
+      <c r="D209" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E209" s="0">
@@ -27914,7 +27914,7 @@
       <c r="C210" s="0" t="n">
         <v>0.279</v>
       </c>
-      <c r="D210" t="n">
+      <c r="D210" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E210" s="0">
@@ -27955,7 +27955,7 @@
       <c r="C211" s="0" t="n">
         <v>0.277</v>
       </c>
-      <c r="D211" t="n">
+      <c r="D211" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E211" s="0">
@@ -27996,7 +27996,7 @@
       <c r="C212" s="0" t="n">
         <v>0.275</v>
       </c>
-      <c r="D212" t="n">
+      <c r="D212" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E212" s="0">
@@ -28037,7 +28037,7 @@
       <c r="C213" s="0" t="n">
         <v>0.272</v>
       </c>
-      <c r="D213" t="n">
+      <c r="D213" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E213" s="0">
@@ -28078,7 +28078,7 @@
       <c r="C214" s="0" t="n">
         <v>0.27</v>
       </c>
-      <c r="D214" t="n">
+      <c r="D214" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E214" s="0">
@@ -28119,7 +28119,7 @@
       <c r="C215" s="0" t="n">
         <v>0.268</v>
       </c>
-      <c r="D215" t="n">
+      <c r="D215" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E215" s="0">
@@ -28160,7 +28160,7 @@
       <c r="C216" s="0" t="n">
         <v>0.265</v>
       </c>
-      <c r="D216" t="n">
+      <c r="D216" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E216" s="0">
@@ -28201,7 +28201,7 @@
       <c r="C217" s="0" t="n">
         <v>0.263</v>
       </c>
-      <c r="D217" t="n">
+      <c r="D217" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E217" s="0">
@@ -28242,7 +28242,7 @@
       <c r="C218" s="0" t="n">
         <v>0.261</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D218" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E218" s="0">
@@ -28283,7 +28283,7 @@
       <c r="C219" s="0" t="n">
         <v>0.259</v>
       </c>
-      <c r="D219" t="n">
+      <c r="D219" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E219" s="0">
@@ -28324,7 +28324,7 @@
       <c r="C220" s="0" t="n">
         <v>0.256</v>
       </c>
-      <c r="D220" t="n">
+      <c r="D220" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E220" s="0">
@@ -28365,7 +28365,7 @@
       <c r="C221" s="0" t="n">
         <v>0.254</v>
       </c>
-      <c r="D221" t="n">
+      <c r="D221" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E221" s="0">
@@ -28406,7 +28406,7 @@
       <c r="C222" s="0" t="n">
         <v>0.252</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D222" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E222" s="0">
@@ -28447,7 +28447,7 @@
       <c r="C223" s="0" t="n">
         <v>0.252</v>
       </c>
-      <c r="D223" t="n">
+      <c r="D223" s="0" t="n">
         <v>0.024</v>
       </c>
       <c r="E223" s="0">
